--- a/standard-observations.xlsx
+++ b/standard-observations.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF107"/>
+  <dimension ref="A1:AP108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,6 +457,16 @@
       <c r="AD1" t="inlineStr"/>
       <c r="AE1" t="inlineStr"/>
       <c r="AF1" t="inlineStr"/>
+      <c r="AG1" t="inlineStr"/>
+      <c r="AH1" t="inlineStr"/>
+      <c r="AI1" t="inlineStr"/>
+      <c r="AJ1" t="inlineStr"/>
+      <c r="AK1" t="inlineStr"/>
+      <c r="AL1" t="inlineStr"/>
+      <c r="AM1" t="inlineStr"/>
+      <c r="AN1" t="inlineStr"/>
+      <c r="AO1" t="inlineStr"/>
+      <c r="AP1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -503,6 +513,16 @@
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -549,6 +569,16 @@
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -595,6 +625,16 @@
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -641,6 +681,16 @@
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -687,6 +737,16 @@
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -733,6 +793,16 @@
       <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -779,6 +849,16 @@
       <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -825,6 +905,16 @@
       <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -871,6 +961,16 @@
       <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -917,6 +1017,16 @@
       <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -963,6 +1073,16 @@
       <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1009,6 +1129,16 @@
       <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1055,6 +1185,16 @@
       <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="inlineStr"/>
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="inlineStr"/>
+      <c r="AP14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1101,6 +1241,16 @@
       <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="inlineStr"/>
+      <c r="AP15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1147,19 +1297,33 @@
       <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr"/>
+      <c r="AJ16" t="inlineStr"/>
+      <c r="AK16" t="inlineStr"/>
+      <c r="AL16" t="inlineStr"/>
+      <c r="AM16" t="inlineStr"/>
+      <c r="AN16" t="inlineStr"/>
+      <c r="AO16" t="inlineStr"/>
+      <c r="AP16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>skos:prefLabel</t>
+          <t>PREFIX</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>eLTER SOs</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
+          <t>doap</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>http://usefulinc.com/ns/doap#</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
@@ -1189,16 +1353,26 @@
       <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr"/>
+      <c r="AJ17" t="inlineStr"/>
+      <c r="AK17" t="inlineStr"/>
+      <c r="AL17" t="inlineStr"/>
+      <c r="AM17" t="inlineStr"/>
+      <c r="AN17" t="inlineStr"/>
+      <c r="AO17" t="inlineStr"/>
+      <c r="AP17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>dct:title</t>
+          <t>skos:prefLabel</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>eLTER Standard Observations</t>
+          <t>eLTER SOs</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
@@ -1231,16 +1405,26 @@
       <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr"/>
+      <c r="AJ18" t="inlineStr"/>
+      <c r="AK18" t="inlineStr"/>
+      <c r="AL18" t="inlineStr"/>
+      <c r="AM18" t="inlineStr"/>
+      <c r="AN18" t="inlineStr"/>
+      <c r="AO18" t="inlineStr"/>
+      <c r="AP18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>dct:description</t>
+          <t>dct:title</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Thesaurus for eLTER Standard Observations</t>
+          <t>eLTER Standard Observations</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
@@ -1273,16 +1457,26 @@
       <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr"/>
+      <c r="AJ19" t="inlineStr"/>
+      <c r="AK19" t="inlineStr"/>
+      <c r="AL19" t="inlineStr"/>
+      <c r="AM19" t="inlineStr"/>
+      <c r="AN19" t="inlineStr"/>
+      <c r="AO19" t="inlineStr"/>
+      <c r="AP19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>dct:creator</t>
+          <t>dct:description</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>http://purl.org/np/RAjk9ru697It_UawXK1gvq-mpaOdGlwyhNb9nF2tfEE2A</t>
+          <t>Thesaurus for eLTER Standard Observations</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
@@ -1315,6 +1509,16 @@
       <c r="AD20" t="inlineStr"/>
       <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr"/>
+      <c r="AJ20" t="inlineStr"/>
+      <c r="AK20" t="inlineStr"/>
+      <c r="AL20" t="inlineStr"/>
+      <c r="AM20" t="inlineStr"/>
+      <c r="AN20" t="inlineStr"/>
+      <c r="AO20" t="inlineStr"/>
+      <c r="AP20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1324,7 +1528,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://orcid.org/0000-0002-7997-219X</t>
+          <t>http://purl.org/np/RAjk9ru697It_UawXK1gvq-mpaOdGlwyhNb9nF2tfEE2A</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
@@ -1357,16 +1561,26 @@
       <c r="AD21" t="inlineStr"/>
       <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr"/>
+      <c r="AJ21" t="inlineStr"/>
+      <c r="AK21" t="inlineStr"/>
+      <c r="AL21" t="inlineStr"/>
+      <c r="AM21" t="inlineStr"/>
+      <c r="AN21" t="inlineStr"/>
+      <c r="AO21" t="inlineStr"/>
+      <c r="AP21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>dct:contributor</t>
+          <t>dct:creator</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://ror.org/013vyke20</t>
+          <t>https://orcid.org/0000-0002-7997-219X</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
@@ -1399,6 +1613,16 @@
       <c r="AD22" t="inlineStr"/>
       <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr"/>
+      <c r="AJ22" t="inlineStr"/>
+      <c r="AK22" t="inlineStr"/>
+      <c r="AL22" t="inlineStr"/>
+      <c r="AM22" t="inlineStr"/>
+      <c r="AN22" t="inlineStr"/>
+      <c r="AO22" t="inlineStr"/>
+      <c r="AP22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1408,7 +1632,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://ror.org/04zaypm56</t>
+          <t>https://ror.org/013vyke20</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
@@ -1441,16 +1665,26 @@
       <c r="AD23" t="inlineStr"/>
       <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr"/>
+      <c r="AJ23" t="inlineStr"/>
+      <c r="AK23" t="inlineStr"/>
+      <c r="AL23" t="inlineStr"/>
+      <c r="AM23" t="inlineStr"/>
+      <c r="AN23" t="inlineStr"/>
+      <c r="AO23" t="inlineStr"/>
+      <c r="AP23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>dct:license</t>
+          <t>dct:contributor</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>https://creativecommons.org/licenses/by/4.0/</t>
+          <t>https://ror.org/04zaypm56</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
@@ -1483,16 +1717,26 @@
       <c r="AD24" t="inlineStr"/>
       <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr"/>
+      <c r="AJ24" t="inlineStr"/>
+      <c r="AK24" t="inlineStr"/>
+      <c r="AL24" t="inlineStr"/>
+      <c r="AM24" t="inlineStr"/>
+      <c r="AN24" t="inlineStr"/>
+      <c r="AO24" t="inlineStr"/>
+      <c r="AP24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>owl:versionInfo</t>
+          <t>dct:license</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1.1.4</t>
+          <t>https://creativecommons.org/licenses/by/4.0/</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
@@ -1525,16 +1769,26 @@
       <c r="AD25" t="inlineStr"/>
       <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr"/>
+      <c r="AJ25" t="inlineStr"/>
+      <c r="AK25" t="inlineStr"/>
+      <c r="AL25" t="inlineStr"/>
+      <c r="AM25" t="inlineStr"/>
+      <c r="AN25" t="inlineStr"/>
+      <c r="AO25" t="inlineStr"/>
+      <c r="AP25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>dct:created</t>
+          <t>owl:versionInfo</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2023-08-16</t>
+          <t>1.1.5</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
@@ -1567,16 +1821,26 @@
       <c r="AD26" t="inlineStr"/>
       <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr"/>
+      <c r="AI26" t="inlineStr"/>
+      <c r="AJ26" t="inlineStr"/>
+      <c r="AK26" t="inlineStr"/>
+      <c r="AL26" t="inlineStr"/>
+      <c r="AM26" t="inlineStr"/>
+      <c r="AN26" t="inlineStr"/>
+      <c r="AO26" t="inlineStr"/>
+      <c r="AP26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>dct:modified</t>
+          <t>dct:created</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2023-08-16</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
@@ -1609,16 +1873,26 @@
       <c r="AD27" t="inlineStr"/>
       <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="inlineStr"/>
+      <c r="AH27" t="inlineStr"/>
+      <c r="AI27" t="inlineStr"/>
+      <c r="AJ27" t="inlineStr"/>
+      <c r="AK27" t="inlineStr"/>
+      <c r="AL27" t="inlineStr"/>
+      <c r="AM27" t="inlineStr"/>
+      <c r="AN27" t="inlineStr"/>
+      <c r="AO27" t="inlineStr"/>
+      <c r="AP27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>owl:ontolgoyIRI</t>
+          <t>dct:modified</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>http://vocabs.lter-europe.net/so/</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
@@ -1651,16 +1925,26 @@
       <c r="AD28" t="inlineStr"/>
       <c r="AE28" t="inlineStr"/>
       <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr"/>
+      <c r="AI28" t="inlineStr"/>
+      <c r="AJ28" t="inlineStr"/>
+      <c r="AK28" t="inlineStr"/>
+      <c r="AL28" t="inlineStr"/>
+      <c r="AM28" t="inlineStr"/>
+      <c r="AN28" t="inlineStr"/>
+      <c r="AO28" t="inlineStr"/>
+      <c r="AP28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>omv:acronym</t>
+          <t>owl:ontolgoyIRI</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SO</t>
+          <t>http://vocabs.lter-europe.net/so/</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
@@ -1693,16 +1977,26 @@
       <c r="AD29" t="inlineStr"/>
       <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr"/>
+      <c r="AI29" t="inlineStr"/>
+      <c r="AJ29" t="inlineStr"/>
+      <c r="AK29" t="inlineStr"/>
+      <c r="AL29" t="inlineStr"/>
+      <c r="AM29" t="inlineStr"/>
+      <c r="AN29" t="inlineStr"/>
+      <c r="AO29" t="inlineStr"/>
+      <c r="AP29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>omv:resourceLocator</t>
+          <t>omv:acronym</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/LTER-Europe/SO/main/standard-observations.ttl</t>
+          <t>SO</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
@@ -1735,16 +2029,26 @@
       <c r="AD30" t="inlineStr"/>
       <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="inlineStr"/>
+      <c r="AH30" t="inlineStr"/>
+      <c r="AI30" t="inlineStr"/>
+      <c r="AJ30" t="inlineStr"/>
+      <c r="AK30" t="inlineStr"/>
+      <c r="AL30" t="inlineStr"/>
+      <c r="AM30" t="inlineStr"/>
+      <c r="AN30" t="inlineStr"/>
+      <c r="AO30" t="inlineStr"/>
+      <c r="AP30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>omv:keywords</t>
+          <t>omv:resourceLocator</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>http://vocabs.lter-europe.net/EnvThes/21672</t>
+          <t>https://raw.githubusercontent.com/LTER-Europe/SO/main/standard-observations.ttl</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
@@ -1777,16 +2081,26 @@
       <c r="AD31" t="inlineStr"/>
       <c r="AE31" t="inlineStr"/>
       <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="inlineStr"/>
+      <c r="AH31" t="inlineStr"/>
+      <c r="AI31" t="inlineStr"/>
+      <c r="AJ31" t="inlineStr"/>
+      <c r="AK31" t="inlineStr"/>
+      <c r="AL31" t="inlineStr"/>
+      <c r="AM31" t="inlineStr"/>
+      <c r="AN31" t="inlineStr"/>
+      <c r="AO31" t="inlineStr"/>
+      <c r="AP31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>dct:publisher</t>
+          <t>omv:keywords</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>https://ror.org/00pggkr55</t>
+          <t>http://vocabs.lter-europe.net/EnvThes/21672</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
@@ -1819,16 +2133,26 @@
       <c r="AD32" t="inlineStr"/>
       <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="inlineStr"/>
+      <c r="AH32" t="inlineStr"/>
+      <c r="AI32" t="inlineStr"/>
+      <c r="AJ32" t="inlineStr"/>
+      <c r="AK32" t="inlineStr"/>
+      <c r="AL32" t="inlineStr"/>
+      <c r="AM32" t="inlineStr"/>
+      <c r="AN32" t="inlineStr"/>
+      <c r="AO32" t="inlineStr"/>
+      <c r="AP32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>omv:knownUsage</t>
+          <t>dct:publisher</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>annotation of observation data</t>
+          <t>https://ror.org/00pggkr55</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
@@ -1861,16 +2185,26 @@
       <c r="AD33" t="inlineStr"/>
       <c r="AE33" t="inlineStr"/>
       <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="inlineStr"/>
+      <c r="AH33" t="inlineStr"/>
+      <c r="AI33" t="inlineStr"/>
+      <c r="AJ33" t="inlineStr"/>
+      <c r="AK33" t="inlineStr"/>
+      <c r="AL33" t="inlineStr"/>
+      <c r="AM33" t="inlineStr"/>
+      <c r="AN33" t="inlineStr"/>
+      <c r="AO33" t="inlineStr"/>
+      <c r="AP33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>dct:audience</t>
+          <t>omv:knownUsage</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>http://schema.org/Researcher</t>
+          <t>annotation of observation data</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
@@ -1903,16 +2237,26 @@
       <c r="AD34" t="inlineStr"/>
       <c r="AE34" t="inlineStr"/>
       <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="inlineStr"/>
+      <c r="AH34" t="inlineStr"/>
+      <c r="AI34" t="inlineStr"/>
+      <c r="AJ34" t="inlineStr"/>
+      <c r="AK34" t="inlineStr"/>
+      <c r="AL34" t="inlineStr"/>
+      <c r="AM34" t="inlineStr"/>
+      <c r="AN34" t="inlineStr"/>
+      <c r="AO34" t="inlineStr"/>
+      <c r="AP34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>doap:repository</t>
+          <t>dct:audience</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>https://ecoportal.lifewatch.eu/ontologies/</t>
+          <t>http://schema.org/Researcher</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
@@ -1945,11 +2289,21 @@
       <c r="AD35" t="inlineStr"/>
       <c r="AE35" t="inlineStr"/>
       <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="inlineStr"/>
+      <c r="AH35" t="inlineStr"/>
+      <c r="AI35" t="inlineStr"/>
+      <c r="AJ35" t="inlineStr"/>
+      <c r="AK35" t="inlineStr"/>
+      <c r="AL35" t="inlineStr"/>
+      <c r="AM35" t="inlineStr"/>
+      <c r="AN35" t="inlineStr"/>
+      <c r="AO35" t="inlineStr"/>
+      <c r="AP35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>schema:includedInDataCatalog</t>
+          <t>doap:repository</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1987,16 +2341,26 @@
       <c r="AD36" t="inlineStr"/>
       <c r="AE36" t="inlineStr"/>
       <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="inlineStr"/>
+      <c r="AH36" t="inlineStr"/>
+      <c r="AI36" t="inlineStr"/>
+      <c r="AJ36" t="inlineStr"/>
+      <c r="AK36" t="inlineStr"/>
+      <c r="AL36" t="inlineStr"/>
+      <c r="AM36" t="inlineStr"/>
+      <c r="AN36" t="inlineStr"/>
+      <c r="AO36" t="inlineStr"/>
+      <c r="AP36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>dct:language</t>
+          <t>schema:includedInDataCatalog</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>en</t>
+          <t>https://ecoportal.lifewatch.eu/ontologies/</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
@@ -2029,16 +2393,26 @@
       <c r="AD37" t="inlineStr"/>
       <c r="AE37" t="inlineStr"/>
       <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="inlineStr"/>
+      <c r="AH37" t="inlineStr"/>
+      <c r="AI37" t="inlineStr"/>
+      <c r="AJ37" t="inlineStr"/>
+      <c r="AK37" t="inlineStr"/>
+      <c r="AL37" t="inlineStr"/>
+      <c r="AM37" t="inlineStr"/>
+      <c r="AN37" t="inlineStr"/>
+      <c r="AO37" t="inlineStr"/>
+      <c r="AP37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>schema:includedInDataCatalog</t>
+          <t>dct:language</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>https://vocabs.lter-europe.net/en/</t>
+          <t>en</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
@@ -2071,113 +2445,47 @@
       <c r="AD38" t="inlineStr"/>
       <c r="AE38" t="inlineStr"/>
       <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="inlineStr"/>
+      <c r="AH38" t="inlineStr"/>
+      <c r="AI38" t="inlineStr"/>
+      <c r="AJ38" t="inlineStr"/>
+      <c r="AK38" t="inlineStr"/>
+      <c r="AL38" t="inlineStr"/>
+      <c r="AM38" t="inlineStr"/>
+      <c r="AN38" t="inlineStr"/>
+      <c r="AO38" t="inlineStr"/>
+      <c r="AP38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Identifier</t>
+          <t>schema:includedInDataCatalog</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>skos:prefLabel@en</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>skos:notation</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>rdf:type(separator=",")</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>skos:definition@en</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>skos:broader(separator=",")</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>dct:source(separator=",")</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>^skos:member</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>skos:exactMatch(separator=",")</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>dct:isReplacedBy</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>skos:closeMatch(separator=",")</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>skos:narrowMatch(separator=",")</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>skos:related(separator=",")</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>obo:RO_0002351(separator=",")</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>skos:broadMatch(separator=",")</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>owl:sameAs(separator=",")</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>rdfs:seeAlso</t>
-        </is>
-      </c>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>dct:creator</t>
-        </is>
-      </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>dct:contributor</t>
-        </is>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>dct:created^^xsd:date</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>dct:modified^^xsd:date</t>
-        </is>
-      </c>
+          <t>https://vocabs.lter-europe.net/en/</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
       <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr"/>
       <c r="X39" t="inlineStr"/>
@@ -2189,63 +2497,121 @@
       <c r="AD39" t="inlineStr"/>
       <c r="AE39" t="inlineStr"/>
       <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="inlineStr"/>
+      <c r="AH39" t="inlineStr"/>
+      <c r="AI39" t="inlineStr"/>
+      <c r="AJ39" t="inlineStr"/>
+      <c r="AK39" t="inlineStr"/>
+      <c r="AL39" t="inlineStr"/>
+      <c r="AM39" t="inlineStr"/>
+      <c r="AN39" t="inlineStr"/>
+      <c r="AO39" t="inlineStr"/>
+      <c r="AP39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>so:027</t>
+          <t>Identifier</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Meteorological data</t>
+          <t>skos:prefLabel@en</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SOATM_027</t>
+          <t>skos:notation</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>skos:Concept, iop:VariableSet</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
+          <t>rdf:type(separator=",")</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>skos:definition@en</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>skos:broader(separator=",")</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>dct:source(separator=",")</t>
+        </is>
+      </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>so:c5</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
+          <t>^skos:member</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>skos:exactMatch(separator=",")</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>dct:isReplacedBy</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>skos:closeMatch(separator=",")</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>skos:narrowMatch(separator=",")</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>skos:related(separator=",")</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>obo:RO_0002351(separator=",")</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>skos:broadMatch(separator=",")</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>owl:sameAs(separator=",")</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>rdfs:seeAlso</t>
+        </is>
+      </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>http://purl.org/np/RAjk9ru697It_UawXK1gvq-mpaOdGlwyhNb9nF2tfEE2A</t>
+          <t>dct:creator</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>https://orcid.org/0000-0003-2195-3997, https://orcid.org/0000-0002-7997-219X</t>
+          <t>dct:contributor</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>8/16/2023</t>
+          <t>dct:created^^xsd:date</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>dct:modified^^xsd:date</t>
         </is>
       </c>
       <c r="V40" t="inlineStr"/>
@@ -2259,21 +2625,31 @@
       <c r="AD40" t="inlineStr"/>
       <c r="AE40" t="inlineStr"/>
       <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="inlineStr"/>
+      <c r="AH40" t="inlineStr"/>
+      <c r="AI40" t="inlineStr"/>
+      <c r="AJ40" t="inlineStr"/>
+      <c r="AK40" t="inlineStr"/>
+      <c r="AL40" t="inlineStr"/>
+      <c r="AM40" t="inlineStr"/>
+      <c r="AN40" t="inlineStr"/>
+      <c r="AO40" t="inlineStr"/>
+      <c r="AP40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>so:028</t>
+          <t>so:027</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Radiation</t>
+          <t>Meteorological data</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>SOATM_028</t>
+          <t>SOATM_027</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2282,13 +2658,13 @@
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>so:c5</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>so:c5</t>
-        </is>
-      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
@@ -2315,7 +2691,7 @@
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="V41" t="inlineStr"/>
@@ -2329,21 +2705,31 @@
       <c r="AD41" t="inlineStr"/>
       <c r="AE41" t="inlineStr"/>
       <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="inlineStr"/>
+      <c r="AH41" t="inlineStr"/>
+      <c r="AI41" t="inlineStr"/>
+      <c r="AJ41" t="inlineStr"/>
+      <c r="AK41" t="inlineStr"/>
+      <c r="AL41" t="inlineStr"/>
+      <c r="AM41" t="inlineStr"/>
+      <c r="AN41" t="inlineStr"/>
+      <c r="AO41" t="inlineStr"/>
+      <c r="AP41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>so:098</t>
+          <t>so:028</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Soil heat flux</t>
+          <t>Radiation</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SOATM_098</t>
+          <t>SOATM_028</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2352,13 +2738,13 @@
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>so:c5</t>
+        </is>
+      </c>
       <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>so:c5</t>
-        </is>
-      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
@@ -2385,7 +2771,7 @@
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="V42" t="inlineStr"/>
@@ -2399,21 +2785,31 @@
       <c r="AD42" t="inlineStr"/>
       <c r="AE42" t="inlineStr"/>
       <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="inlineStr"/>
+      <c r="AH42" t="inlineStr"/>
+      <c r="AI42" t="inlineStr"/>
+      <c r="AJ42" t="inlineStr"/>
+      <c r="AK42" t="inlineStr"/>
+      <c r="AL42" t="inlineStr"/>
+      <c r="AM42" t="inlineStr"/>
+      <c r="AN42" t="inlineStr"/>
+      <c r="AO42" t="inlineStr"/>
+      <c r="AP42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>so:103</t>
+          <t>so:098</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Atmospheric deposition in precipitation</t>
+          <t>Soil heat flux</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SOATM_103</t>
+          <t>SOATM_098</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2422,13 +2818,13 @@
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>so:c5</t>
+        </is>
+      </c>
       <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>so:c5</t>
-        </is>
-      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
@@ -2455,7 +2851,7 @@
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>2023-08-23</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="V43" t="inlineStr"/>
@@ -2469,21 +2865,31 @@
       <c r="AD43" t="inlineStr"/>
       <c r="AE43" t="inlineStr"/>
       <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="inlineStr"/>
+      <c r="AH43" t="inlineStr"/>
+      <c r="AI43" t="inlineStr"/>
+      <c r="AJ43" t="inlineStr"/>
+      <c r="AK43" t="inlineStr"/>
+      <c r="AL43" t="inlineStr"/>
+      <c r="AM43" t="inlineStr"/>
+      <c r="AN43" t="inlineStr"/>
+      <c r="AO43" t="inlineStr"/>
+      <c r="AP43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>so:108</t>
+          <t>so:103</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Dry deposition of N-components</t>
+          <t>Atmospheric deposition in precipitation</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SOATM_108</t>
+          <t>SOATM_103</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2492,13 +2898,13 @@
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>so:c5</t>
+        </is>
+      </c>
       <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>so:c5</t>
-        </is>
-      </c>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
@@ -2525,7 +2931,7 @@
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>2023-08-23</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="V44" t="inlineStr"/>
@@ -2539,21 +2945,31 @@
       <c r="AD44" t="inlineStr"/>
       <c r="AE44" t="inlineStr"/>
       <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="inlineStr"/>
+      <c r="AH44" t="inlineStr"/>
+      <c r="AI44" t="inlineStr"/>
+      <c r="AJ44" t="inlineStr"/>
+      <c r="AK44" t="inlineStr"/>
+      <c r="AL44" t="inlineStr"/>
+      <c r="AM44" t="inlineStr"/>
+      <c r="AN44" t="inlineStr"/>
+      <c r="AO44" t="inlineStr"/>
+      <c r="AP44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>so:176</t>
+          <t>so:108</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Eddy Covariance (CO2 flux and concentration, Latent heat flux, Sensible heat flux)</t>
+          <t>Dry deposition of N-components</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>SOATM_176</t>
+          <t>SOATM_108</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2562,13 +2978,13 @@
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>so:c5</t>
+        </is>
+      </c>
       <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>so:c5</t>
-        </is>
-      </c>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
@@ -2595,7 +3011,7 @@
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="V45" t="inlineStr"/>
@@ -2609,21 +3025,31 @@
       <c r="AD45" t="inlineStr"/>
       <c r="AE45" t="inlineStr"/>
       <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="inlineStr"/>
+      <c r="AH45" t="inlineStr"/>
+      <c r="AI45" t="inlineStr"/>
+      <c r="AJ45" t="inlineStr"/>
+      <c r="AK45" t="inlineStr"/>
+      <c r="AL45" t="inlineStr"/>
+      <c r="AM45" t="inlineStr"/>
+      <c r="AN45" t="inlineStr"/>
+      <c r="AO45" t="inlineStr"/>
+      <c r="AP45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>so:014</t>
+          <t>so:176</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Flying insects</t>
+          <t>Eddy Covariance (CO2 flux and concentration, Latent heat flux, Sensible heat flux)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>SOBIO_014</t>
+          <t>SOATM_176</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2632,13 +3058,13 @@
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>so:c5</t>
+        </is>
+      </c>
       <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>so:c4</t>
-        </is>
-      </c>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
@@ -2665,7 +3091,7 @@
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>2023-08-23</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="V46" t="inlineStr"/>
@@ -2679,21 +3105,31 @@
       <c r="AD46" t="inlineStr"/>
       <c r="AE46" t="inlineStr"/>
       <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="inlineStr"/>
+      <c r="AH46" t="inlineStr"/>
+      <c r="AI46" t="inlineStr"/>
+      <c r="AJ46" t="inlineStr"/>
+      <c r="AK46" t="inlineStr"/>
+      <c r="AL46" t="inlineStr"/>
+      <c r="AM46" t="inlineStr"/>
+      <c r="AN46" t="inlineStr"/>
+      <c r="AO46" t="inlineStr"/>
+      <c r="AP46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>so:015</t>
+          <t>so:014</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Vegetation phenology and Leaf Area Index - European scale</t>
+          <t>Flying insects</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SOBIO_015</t>
+          <t>SOBIO_014</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2702,13 +3138,13 @@
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>so:c4</t>
+        </is>
+      </c>
       <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>so:c5</t>
-        </is>
-      </c>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
@@ -2735,7 +3171,7 @@
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="V47" t="inlineStr"/>
@@ -2749,21 +3185,31 @@
       <c r="AD47" t="inlineStr"/>
       <c r="AE47" t="inlineStr"/>
       <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="inlineStr"/>
+      <c r="AH47" t="inlineStr"/>
+      <c r="AI47" t="inlineStr"/>
+      <c r="AJ47" t="inlineStr"/>
+      <c r="AK47" t="inlineStr"/>
+      <c r="AL47" t="inlineStr"/>
+      <c r="AM47" t="inlineStr"/>
+      <c r="AN47" t="inlineStr"/>
+      <c r="AO47" t="inlineStr"/>
+      <c r="AP47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>so:016</t>
+          <t>so:015</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Vegetation phenology - site scale</t>
+          <t>Vegetation phenology and Leaf Area Index - European scale</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>SOBIO_016</t>
+          <t>SOBIO_015</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2772,13 +3218,13 @@
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>so:c5</t>
+        </is>
+      </c>
       <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>so:c5</t>
-        </is>
-      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
@@ -2805,7 +3251,7 @@
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="V48" t="inlineStr"/>
@@ -2819,21 +3265,31 @@
       <c r="AD48" t="inlineStr"/>
       <c r="AE48" t="inlineStr"/>
       <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="inlineStr"/>
+      <c r="AH48" t="inlineStr"/>
+      <c r="AI48" t="inlineStr"/>
+      <c r="AJ48" t="inlineStr"/>
+      <c r="AK48" t="inlineStr"/>
+      <c r="AL48" t="inlineStr"/>
+      <c r="AM48" t="inlineStr"/>
+      <c r="AN48" t="inlineStr"/>
+      <c r="AO48" t="inlineStr"/>
+      <c r="AP48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>so:017</t>
+          <t>so:016</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Vegetation composition (mainly species level+abundance)</t>
+          <t>Vegetation phenology - site scale</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SOBIO_017</t>
+          <t>SOBIO_016</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2842,13 +3298,13 @@
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>so:c5</t>
+        </is>
+      </c>
       <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>so:c4</t>
-        </is>
-      </c>
+      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
@@ -2875,7 +3331,7 @@
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>2023-08-23</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="V49" t="inlineStr"/>
@@ -2889,21 +3345,31 @@
       <c r="AD49" t="inlineStr"/>
       <c r="AE49" t="inlineStr"/>
       <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="inlineStr"/>
+      <c r="AH49" t="inlineStr"/>
+      <c r="AI49" t="inlineStr"/>
+      <c r="AJ49" t="inlineStr"/>
+      <c r="AK49" t="inlineStr"/>
+      <c r="AL49" t="inlineStr"/>
+      <c r="AM49" t="inlineStr"/>
+      <c r="AN49" t="inlineStr"/>
+      <c r="AO49" t="inlineStr"/>
+      <c r="AP49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>so:018</t>
+          <t>so:017</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Birds, bats, frogs, insects using acoustic recording</t>
+          <t>Vegetation composition (mainly species level+abundance)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SOBIO_018</t>
+          <t>SOBIO_017</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2912,13 +3378,13 @@
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>so:c4</t>
+        </is>
+      </c>
       <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>so:c4</t>
-        </is>
-      </c>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
@@ -2945,7 +3411,7 @@
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>2023-08-23</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="V50" t="inlineStr"/>
@@ -2959,21 +3425,31 @@
       <c r="AD50" t="inlineStr"/>
       <c r="AE50" t="inlineStr"/>
       <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="inlineStr"/>
+      <c r="AH50" t="inlineStr"/>
+      <c r="AI50" t="inlineStr"/>
+      <c r="AJ50" t="inlineStr"/>
+      <c r="AK50" t="inlineStr"/>
+      <c r="AL50" t="inlineStr"/>
+      <c r="AM50" t="inlineStr"/>
+      <c r="AN50" t="inlineStr"/>
+      <c r="AO50" t="inlineStr"/>
+      <c r="AP50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>so:019</t>
+          <t>so:018</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Pollen and spores</t>
+          <t>Birds, bats, frogs, insects using acoustic recording</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>SOBIO_019</t>
+          <t>SOBIO_018</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2982,13 +3458,13 @@
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>so:c4</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>so:c4</t>
-        </is>
-      </c>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
@@ -3015,7 +3491,7 @@
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>2023-08-23</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="V51" t="inlineStr"/>
@@ -3029,21 +3505,31 @@
       <c r="AD51" t="inlineStr"/>
       <c r="AE51" t="inlineStr"/>
       <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="inlineStr"/>
+      <c r="AH51" t="inlineStr"/>
+      <c r="AI51" t="inlineStr"/>
+      <c r="AJ51" t="inlineStr"/>
+      <c r="AK51" t="inlineStr"/>
+      <c r="AL51" t="inlineStr"/>
+      <c r="AM51" t="inlineStr"/>
+      <c r="AN51" t="inlineStr"/>
+      <c r="AO51" t="inlineStr"/>
+      <c r="AP51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>so:021</t>
+          <t>so:019</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>eDNA Water</t>
+          <t>Pollen and spores</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>SOBIO_021</t>
+          <t>SOBIO_019</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3052,13 +3538,13 @@
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>so:c4</t>
+        </is>
+      </c>
       <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>so:c4</t>
-        </is>
-      </c>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
@@ -3085,7 +3571,7 @@
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="V52" t="inlineStr"/>
@@ -3099,21 +3585,31 @@
       <c r="AD52" t="inlineStr"/>
       <c r="AE52" t="inlineStr"/>
       <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="inlineStr"/>
+      <c r="AH52" t="inlineStr"/>
+      <c r="AI52" t="inlineStr"/>
+      <c r="AJ52" t="inlineStr"/>
+      <c r="AK52" t="inlineStr"/>
+      <c r="AL52" t="inlineStr"/>
+      <c r="AM52" t="inlineStr"/>
+      <c r="AN52" t="inlineStr"/>
+      <c r="AO52" t="inlineStr"/>
+      <c r="AP52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>so:022</t>
+          <t>so:021</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>eDNA soil</t>
+          <t>eDNA Water</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>SOBIO_022</t>
+          <t>SOBIO_021</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3122,13 +3618,13 @@
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>so:c4</t>
+        </is>
+      </c>
       <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>so:c4</t>
-        </is>
-      </c>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
@@ -3155,7 +3651,7 @@
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="V53" t="inlineStr"/>
@@ -3169,21 +3665,31 @@
       <c r="AD53" t="inlineStr"/>
       <c r="AE53" t="inlineStr"/>
       <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="inlineStr"/>
+      <c r="AH53" t="inlineStr"/>
+      <c r="AI53" t="inlineStr"/>
+      <c r="AJ53" t="inlineStr"/>
+      <c r="AK53" t="inlineStr"/>
+      <c r="AL53" t="inlineStr"/>
+      <c r="AM53" t="inlineStr"/>
+      <c r="AN53" t="inlineStr"/>
+      <c r="AO53" t="inlineStr"/>
+      <c r="AP53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>so:023</t>
+          <t>so:022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Vegetation aboveground biomass - forest (site scale)</t>
+          <t>eDNA soil</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>SOATM_023</t>
+          <t>SOBIO_022</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3192,13 +3698,13 @@
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>so:c4</t>
+        </is>
+      </c>
       <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>so:c5</t>
-        </is>
-      </c>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
@@ -3225,7 +3731,7 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="V54" t="inlineStr"/>
@@ -3239,21 +3745,31 @@
       <c r="AD54" t="inlineStr"/>
       <c r="AE54" t="inlineStr"/>
       <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="inlineStr"/>
+      <c r="AH54" t="inlineStr"/>
+      <c r="AI54" t="inlineStr"/>
+      <c r="AJ54" t="inlineStr"/>
+      <c r="AK54" t="inlineStr"/>
+      <c r="AL54" t="inlineStr"/>
+      <c r="AM54" t="inlineStr"/>
+      <c r="AN54" t="inlineStr"/>
+      <c r="AO54" t="inlineStr"/>
+      <c r="AP54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>so:024</t>
+          <t>so:023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Vegetation aboveground biomass - non-forested sites</t>
+          <t>Vegetation aboveground biomass - forest (site scale)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>SOATM_024</t>
+          <t>SOATM_023</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3262,13 +3778,13 @@
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>so:c5</t>
+        </is>
+      </c>
       <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>so:c5</t>
-        </is>
-      </c>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
@@ -3295,7 +3811,7 @@
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="V55" t="inlineStr"/>
@@ -3309,21 +3825,31 @@
       <c r="AD55" t="inlineStr"/>
       <c r="AE55" t="inlineStr"/>
       <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="inlineStr"/>
+      <c r="AH55" t="inlineStr"/>
+      <c r="AI55" t="inlineStr"/>
+      <c r="AJ55" t="inlineStr"/>
+      <c r="AK55" t="inlineStr"/>
+      <c r="AL55" t="inlineStr"/>
+      <c r="AM55" t="inlineStr"/>
+      <c r="AN55" t="inlineStr"/>
+      <c r="AO55" t="inlineStr"/>
+      <c r="AP55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>so:025</t>
+          <t>so:024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Leaf area index - forests (site scale)</t>
+          <t>Vegetation aboveground biomass - non-forested sites</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>SOATM_025</t>
+          <t>SOATM_024</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3332,13 +3858,13 @@
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>so:c5</t>
+        </is>
+      </c>
       <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>so:c5</t>
-        </is>
-      </c>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
@@ -3365,7 +3891,7 @@
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="V56" t="inlineStr"/>
@@ -3379,21 +3905,31 @@
       <c r="AD56" t="inlineStr"/>
       <c r="AE56" t="inlineStr"/>
       <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="inlineStr"/>
+      <c r="AH56" t="inlineStr"/>
+      <c r="AI56" t="inlineStr"/>
+      <c r="AJ56" t="inlineStr"/>
+      <c r="AK56" t="inlineStr"/>
+      <c r="AL56" t="inlineStr"/>
+      <c r="AM56" t="inlineStr"/>
+      <c r="AN56" t="inlineStr"/>
+      <c r="AO56" t="inlineStr"/>
+      <c r="AP56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>so:026</t>
+          <t>so:025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Leaf area index - non-forested sites</t>
+          <t>Leaf area index - forests (site scale)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SOATM_026</t>
+          <t>SOATM_025</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3402,13 +3938,13 @@
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>so:c5</t>
+        </is>
+      </c>
       <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>so:c5</t>
-        </is>
-      </c>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
@@ -3435,7 +3971,7 @@
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="V57" t="inlineStr"/>
@@ -3449,21 +3985,31 @@
       <c r="AD57" t="inlineStr"/>
       <c r="AE57" t="inlineStr"/>
       <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="inlineStr"/>
+      <c r="AH57" t="inlineStr"/>
+      <c r="AI57" t="inlineStr"/>
+      <c r="AJ57" t="inlineStr"/>
+      <c r="AK57" t="inlineStr"/>
+      <c r="AL57" t="inlineStr"/>
+      <c r="AM57" t="inlineStr"/>
+      <c r="AN57" t="inlineStr"/>
+      <c r="AO57" t="inlineStr"/>
+      <c r="AP57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>so:090</t>
+          <t>so:026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Gross primary production</t>
+          <t>Leaf area index - non-forested sites</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SOATM_090</t>
+          <t>SOATM_026</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3472,13 +4018,13 @@
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>so:c5</t>
+        </is>
+      </c>
       <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>so:c5</t>
-        </is>
-      </c>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
@@ -3505,7 +4051,7 @@
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="V58" t="inlineStr"/>
@@ -3519,21 +4065,31 @@
       <c r="AD58" t="inlineStr"/>
       <c r="AE58" t="inlineStr"/>
       <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="inlineStr"/>
+      <c r="AH58" t="inlineStr"/>
+      <c r="AI58" t="inlineStr"/>
+      <c r="AJ58" t="inlineStr"/>
+      <c r="AK58" t="inlineStr"/>
+      <c r="AL58" t="inlineStr"/>
+      <c r="AM58" t="inlineStr"/>
+      <c r="AN58" t="inlineStr"/>
+      <c r="AO58" t="inlineStr"/>
+      <c r="AP58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>so:091</t>
+          <t>so:090</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Transpiration (plants)</t>
+          <t>Gross primary production</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>SOATM_091</t>
+          <t>SOATM_090</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3542,13 +4098,13 @@
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>so:c5</t>
+        </is>
+      </c>
       <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>so:c5</t>
-        </is>
-      </c>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
@@ -3575,7 +4131,7 @@
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="V59" t="inlineStr"/>
@@ -3589,21 +4145,31 @@
       <c r="AD59" t="inlineStr"/>
       <c r="AE59" t="inlineStr"/>
       <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="inlineStr"/>
+      <c r="AH59" t="inlineStr"/>
+      <c r="AI59" t="inlineStr"/>
+      <c r="AJ59" t="inlineStr"/>
+      <c r="AK59" t="inlineStr"/>
+      <c r="AL59" t="inlineStr"/>
+      <c r="AM59" t="inlineStr"/>
+      <c r="AN59" t="inlineStr"/>
+      <c r="AO59" t="inlineStr"/>
+      <c r="AP59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>so:092</t>
+          <t>so:091</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Aboveground litterfall - forests</t>
+          <t>Transpiration (plants)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>SOATM_092</t>
+          <t>SOATM_091</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3612,13 +4178,13 @@
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>so:c5</t>
+        </is>
+      </c>
       <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>so:c5</t>
-        </is>
-      </c>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
@@ -3645,7 +4211,7 @@
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="V60" t="inlineStr"/>
@@ -3659,21 +4225,31 @@
       <c r="AD60" t="inlineStr"/>
       <c r="AE60" t="inlineStr"/>
       <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="inlineStr"/>
+      <c r="AH60" t="inlineStr"/>
+      <c r="AI60" t="inlineStr"/>
+      <c r="AJ60" t="inlineStr"/>
+      <c r="AK60" t="inlineStr"/>
+      <c r="AL60" t="inlineStr"/>
+      <c r="AM60" t="inlineStr"/>
+      <c r="AN60" t="inlineStr"/>
+      <c r="AO60" t="inlineStr"/>
+      <c r="AP60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>so:095</t>
+          <t>so:092</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Leaf C, N, K, P, Ca, Mg, Mn content - terrestrial</t>
+          <t>Aboveground litterfall - forests</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>SOATM_095</t>
+          <t>SOATM_092</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3682,13 +4258,13 @@
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>so:c5</t>
+        </is>
+      </c>
       <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>so:c5</t>
-        </is>
-      </c>
+      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
@@ -3715,7 +4291,7 @@
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="V61" t="inlineStr"/>
@@ -3729,21 +4305,31 @@
       <c r="AD61" t="inlineStr"/>
       <c r="AE61" t="inlineStr"/>
       <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="inlineStr"/>
+      <c r="AH61" t="inlineStr"/>
+      <c r="AI61" t="inlineStr"/>
+      <c r="AJ61" t="inlineStr"/>
+      <c r="AK61" t="inlineStr"/>
+      <c r="AL61" t="inlineStr"/>
+      <c r="AM61" t="inlineStr"/>
+      <c r="AN61" t="inlineStr"/>
+      <c r="AO61" t="inlineStr"/>
+      <c r="AP61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>so:096</t>
+          <t>so:095</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Clorophyll a (benthic, pelagic) - standing, running waters</t>
+          <t>Leaf C, N, K, P, Ca, Mg, Mn content - terrestrial</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>SOBIO_096</t>
+          <t>SOATM_095</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3752,13 +4338,13 @@
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>so:c5</t>
+        </is>
+      </c>
       <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>so:c4</t>
-        </is>
-      </c>
+      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
@@ -3785,7 +4371,7 @@
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>2023-08-23</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="V62" t="inlineStr"/>
@@ -3799,21 +4385,31 @@
       <c r="AD62" t="inlineStr"/>
       <c r="AE62" t="inlineStr"/>
       <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="inlineStr"/>
+      <c r="AH62" t="inlineStr"/>
+      <c r="AI62" t="inlineStr"/>
+      <c r="AJ62" t="inlineStr"/>
+      <c r="AK62" t="inlineStr"/>
+      <c r="AL62" t="inlineStr"/>
+      <c r="AM62" t="inlineStr"/>
+      <c r="AN62" t="inlineStr"/>
+      <c r="AO62" t="inlineStr"/>
+      <c r="AP62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>so:140</t>
+          <t>so:096</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Vegetation structure - site scale</t>
+          <t>Clorophyll a (benthic, pelagic) - standing, running waters</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>SOATM_140</t>
+          <t>SOBIO_096</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3822,13 +4418,13 @@
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>so:c4</t>
+        </is>
+      </c>
       <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>so:c5</t>
-        </is>
-      </c>
+      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
@@ -3855,7 +4451,7 @@
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="V63" t="inlineStr"/>
@@ -3869,21 +4465,31 @@
       <c r="AD63" t="inlineStr"/>
       <c r="AE63" t="inlineStr"/>
       <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="inlineStr"/>
+      <c r="AH63" t="inlineStr"/>
+      <c r="AI63" t="inlineStr"/>
+      <c r="AJ63" t="inlineStr"/>
+      <c r="AK63" t="inlineStr"/>
+      <c r="AL63" t="inlineStr"/>
+      <c r="AM63" t="inlineStr"/>
+      <c r="AN63" t="inlineStr"/>
+      <c r="AO63" t="inlineStr"/>
+      <c r="AP63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>so:177</t>
+          <t>so:140</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Tree growth</t>
+          <t>Vegetation structure - site scale</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>SOATM_177</t>
+          <t>SOATM_140</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3892,13 +4498,13 @@
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>so:c5</t>
+        </is>
+      </c>
       <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>so:c5</t>
-        </is>
-      </c>
+      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
@@ -3925,7 +4531,7 @@
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="V64" t="inlineStr"/>
@@ -3939,21 +4545,31 @@
       <c r="AD64" t="inlineStr"/>
       <c r="AE64" t="inlineStr"/>
       <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="inlineStr"/>
+      <c r="AH64" t="inlineStr"/>
+      <c r="AI64" t="inlineStr"/>
+      <c r="AJ64" t="inlineStr"/>
+      <c r="AK64" t="inlineStr"/>
+      <c r="AL64" t="inlineStr"/>
+      <c r="AM64" t="inlineStr"/>
+      <c r="AN64" t="inlineStr"/>
+      <c r="AO64" t="inlineStr"/>
+      <c r="AP64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>so:003</t>
+          <t>so:177</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Soil chemical and physical characteristics</t>
+          <t>Tree growth</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>SOGEO_003</t>
+          <t>SOATM_177</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3962,13 +4578,13 @@
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>so:c5</t>
+        </is>
+      </c>
       <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>so:c2</t>
-        </is>
-      </c>
+      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
@@ -3995,7 +4611,7 @@
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>2023-08-23</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="V65" t="inlineStr"/>
@@ -4009,21 +4625,31 @@
       <c r="AD65" t="inlineStr"/>
       <c r="AE65" t="inlineStr"/>
       <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="inlineStr"/>
+      <c r="AH65" t="inlineStr"/>
+      <c r="AI65" t="inlineStr"/>
+      <c r="AJ65" t="inlineStr"/>
+      <c r="AK65" t="inlineStr"/>
+      <c r="AL65" t="inlineStr"/>
+      <c r="AM65" t="inlineStr"/>
+      <c r="AN65" t="inlineStr"/>
+      <c r="AO65" t="inlineStr"/>
+      <c r="AP65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>so:048</t>
+          <t>so:003</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Percolation/infiltration - soil</t>
+          <t>Soil chemical and physical characteristics</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>SOGEO_048</t>
+          <t>SOGEO_003</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4032,13 +4658,13 @@
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>so:c2</t>
+        </is>
+      </c>
       <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>so:c2</t>
-        </is>
-      </c>
+      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
@@ -4065,7 +4691,7 @@
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>2023-08-23</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="V66" t="inlineStr"/>
@@ -4079,21 +4705,31 @@
       <c r="AD66" t="inlineStr"/>
       <c r="AE66" t="inlineStr"/>
       <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="inlineStr"/>
+      <c r="AH66" t="inlineStr"/>
+      <c r="AI66" t="inlineStr"/>
+      <c r="AJ66" t="inlineStr"/>
+      <c r="AK66" t="inlineStr"/>
+      <c r="AL66" t="inlineStr"/>
+      <c r="AM66" t="inlineStr"/>
+      <c r="AN66" t="inlineStr"/>
+      <c r="AO66" t="inlineStr"/>
+      <c r="AP66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>so:155</t>
+          <t>so:048</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Sediment (aquatic and marine) inventory</t>
+          <t>Percolation/infiltration - soil</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>SOGEO_155</t>
+          <t>SOGEO_048</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4102,13 +4738,13 @@
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>so:c2</t>
+        </is>
+      </c>
       <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>so:c2</t>
-        </is>
-      </c>
+      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
@@ -4135,7 +4771,7 @@
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>2023-08-23</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="V67" t="inlineStr"/>
@@ -4149,21 +4785,31 @@
       <c r="AD67" t="inlineStr"/>
       <c r="AE67" t="inlineStr"/>
       <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="inlineStr"/>
+      <c r="AH67" t="inlineStr"/>
+      <c r="AI67" t="inlineStr"/>
+      <c r="AJ67" t="inlineStr"/>
+      <c r="AK67" t="inlineStr"/>
+      <c r="AL67" t="inlineStr"/>
+      <c r="AM67" t="inlineStr"/>
+      <c r="AN67" t="inlineStr"/>
+      <c r="AO67" t="inlineStr"/>
+      <c r="AP67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>so:167</t>
+          <t>so:155</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Soil water chemical characteristics</t>
+          <t>Sediment (aquatic and marine) inventory</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>SOGEO_167</t>
+          <t>SOGEO_155</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4172,13 +4818,13 @@
         </is>
       </c>
       <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>so:c2</t>
+        </is>
+      </c>
       <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>so:c2</t>
-        </is>
-      </c>
+      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
@@ -4205,7 +4851,7 @@
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>2023-08-23</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="V68" t="inlineStr"/>
@@ -4219,21 +4865,31 @@
       <c r="AD68" t="inlineStr"/>
       <c r="AE68" t="inlineStr"/>
       <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="inlineStr"/>
+      <c r="AH68" t="inlineStr"/>
+      <c r="AI68" t="inlineStr"/>
+      <c r="AJ68" t="inlineStr"/>
+      <c r="AK68" t="inlineStr"/>
+      <c r="AL68" t="inlineStr"/>
+      <c r="AM68" t="inlineStr"/>
+      <c r="AN68" t="inlineStr"/>
+      <c r="AO68" t="inlineStr"/>
+      <c r="AP68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>so:004</t>
+          <t>so:167</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Profiles of physical and chemical waters characteristics - surface water (standing)</t>
+          <t>Soil water chemical characteristics</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SOHYD_004</t>
+          <t>SOGEO_167</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4242,13 +4898,13 @@
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>so:c2</t>
+        </is>
+      </c>
       <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>so:c3</t>
-        </is>
-      </c>
+      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
@@ -4275,7 +4931,7 @@
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>2023-08-23</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="V69" t="inlineStr"/>
@@ -4289,21 +4945,31 @@
       <c r="AD69" t="inlineStr"/>
       <c r="AE69" t="inlineStr"/>
       <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="inlineStr"/>
+      <c r="AH69" t="inlineStr"/>
+      <c r="AI69" t="inlineStr"/>
+      <c r="AJ69" t="inlineStr"/>
+      <c r="AK69" t="inlineStr"/>
+      <c r="AL69" t="inlineStr"/>
+      <c r="AM69" t="inlineStr"/>
+      <c r="AN69" t="inlineStr"/>
+      <c r="AO69" t="inlineStr"/>
+      <c r="AP69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>so:005</t>
+          <t>so:004</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Physical and chemical water characteristics - surface water (running waters)</t>
+          <t>Profiles of physical and chemical waters characteristics - surface water (standing)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>SOHYD_005</t>
+          <t>SOHYD_004</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4312,13 +4978,13 @@
         </is>
       </c>
       <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>so:c3</t>
+        </is>
+      </c>
       <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>so:c3</t>
-        </is>
-      </c>
+      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
@@ -4345,7 +5011,7 @@
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>2023-08-23</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="V70" t="inlineStr"/>
@@ -4359,21 +5025,31 @@
       <c r="AD70" t="inlineStr"/>
       <c r="AE70" t="inlineStr"/>
       <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="inlineStr"/>
+      <c r="AH70" t="inlineStr"/>
+      <c r="AI70" t="inlineStr"/>
+      <c r="AJ70" t="inlineStr"/>
+      <c r="AK70" t="inlineStr"/>
+      <c r="AL70" t="inlineStr"/>
+      <c r="AM70" t="inlineStr"/>
+      <c r="AN70" t="inlineStr"/>
+      <c r="AO70" t="inlineStr"/>
+      <c r="AP70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>so:006</t>
+          <t>so:005</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Physical and chemical water characteristics - groundwater</t>
+          <t>Physical and chemical water characteristics - surface water (running waters)</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>SOHYD_006</t>
+          <t>SOHYD_005</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4382,13 +5058,13 @@
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>so:c3</t>
+        </is>
+      </c>
       <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>so:c3</t>
-        </is>
-      </c>
+      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
@@ -4415,7 +5091,7 @@
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>2023-08-23</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="V71" t="inlineStr"/>
@@ -4429,21 +5105,31 @@
       <c r="AD71" t="inlineStr"/>
       <c r="AE71" t="inlineStr"/>
       <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="inlineStr"/>
+      <c r="AH71" t="inlineStr"/>
+      <c r="AI71" t="inlineStr"/>
+      <c r="AJ71" t="inlineStr"/>
+      <c r="AK71" t="inlineStr"/>
+      <c r="AL71" t="inlineStr"/>
+      <c r="AM71" t="inlineStr"/>
+      <c r="AN71" t="inlineStr"/>
+      <c r="AO71" t="inlineStr"/>
+      <c r="AP71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>so:010</t>
+          <t>so:006</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Water level - surface water (running water)</t>
+          <t>Physical and chemical water characteristics - groundwater</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>SOHYD_010</t>
+          <t>SOHYD_006</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4452,13 +5138,13 @@
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>so:c3</t>
+        </is>
+      </c>
       <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>so:c3</t>
-        </is>
-      </c>
+      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
@@ -4485,7 +5171,7 @@
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>2023-08-23</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="V72" t="inlineStr"/>
@@ -4499,21 +5185,31 @@
       <c r="AD72" t="inlineStr"/>
       <c r="AE72" t="inlineStr"/>
       <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="inlineStr"/>
+      <c r="AH72" t="inlineStr"/>
+      <c r="AI72" t="inlineStr"/>
+      <c r="AJ72" t="inlineStr"/>
+      <c r="AK72" t="inlineStr"/>
+      <c r="AL72" t="inlineStr"/>
+      <c r="AM72" t="inlineStr"/>
+      <c r="AN72" t="inlineStr"/>
+      <c r="AO72" t="inlineStr"/>
+      <c r="AP72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>so:011</t>
+          <t>so:010</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Ice cover/thickness (standing and transitional water)</t>
+          <t>Water level - surface water (running water)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>SOHYD_011</t>
+          <t>SOHYD_010</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4522,13 +5218,13 @@
         </is>
       </c>
       <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>so:c3</t>
+        </is>
+      </c>
       <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>so:c3</t>
-        </is>
-      </c>
+      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
@@ -4555,7 +5251,7 @@
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>2023-08-23</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="V73" t="inlineStr"/>
@@ -4569,21 +5265,31 @@
       <c r="AD73" t="inlineStr"/>
       <c r="AE73" t="inlineStr"/>
       <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="inlineStr"/>
+      <c r="AH73" t="inlineStr"/>
+      <c r="AI73" t="inlineStr"/>
+      <c r="AJ73" t="inlineStr"/>
+      <c r="AK73" t="inlineStr"/>
+      <c r="AL73" t="inlineStr"/>
+      <c r="AM73" t="inlineStr"/>
+      <c r="AN73" t="inlineStr"/>
+      <c r="AO73" t="inlineStr"/>
+      <c r="AP73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>so:012</t>
+          <t>so:011</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Snow cover and depths</t>
+          <t>Ice cover/thickness (standing and transitional water)</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>SOHYD_012</t>
+          <t>SOHYD_011</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4592,13 +5298,13 @@
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>so:c3</t>
+        </is>
+      </c>
       <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>so:c3</t>
-        </is>
-      </c>
+      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
@@ -4625,7 +5331,7 @@
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>2023-08-23</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="V74" t="inlineStr"/>
@@ -4639,21 +5345,31 @@
       <c r="AD74" t="inlineStr"/>
       <c r="AE74" t="inlineStr"/>
       <c r="AF74" t="inlineStr"/>
+      <c r="AG74" t="inlineStr"/>
+      <c r="AH74" t="inlineStr"/>
+      <c r="AI74" t="inlineStr"/>
+      <c r="AJ74" t="inlineStr"/>
+      <c r="AK74" t="inlineStr"/>
+      <c r="AL74" t="inlineStr"/>
+      <c r="AM74" t="inlineStr"/>
+      <c r="AN74" t="inlineStr"/>
+      <c r="AO74" t="inlineStr"/>
+      <c r="AP74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>so:058</t>
+          <t>so:012</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Stable isotopes (18O, 2H) - standing, running waters</t>
+          <t>Snow cover and depths</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>SOHYD_058</t>
+          <t>SOHYD_012</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4662,13 +5378,13 @@
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>so:c3</t>
+        </is>
+      </c>
       <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>so:c3</t>
-        </is>
-      </c>
+      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
@@ -4695,7 +5411,7 @@
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="V75" t="inlineStr"/>
@@ -4709,21 +5425,31 @@
       <c r="AD75" t="inlineStr"/>
       <c r="AE75" t="inlineStr"/>
       <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="inlineStr"/>
+      <c r="AH75" t="inlineStr"/>
+      <c r="AI75" t="inlineStr"/>
+      <c r="AJ75" t="inlineStr"/>
+      <c r="AK75" t="inlineStr"/>
+      <c r="AL75" t="inlineStr"/>
+      <c r="AM75" t="inlineStr"/>
+      <c r="AN75" t="inlineStr"/>
+      <c r="AO75" t="inlineStr"/>
+      <c r="AP75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>so:059</t>
+          <t>so:058</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Stable Isotopes (18O, 2H) - groundwater</t>
+          <t>Stable isotopes (18O, 2H) - standing, running waters</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>SOHYD_059</t>
+          <t>SOHYD_058</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4732,13 +5458,13 @@
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>so:c3</t>
+        </is>
+      </c>
       <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>so:c3</t>
-        </is>
-      </c>
+      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
@@ -4765,7 +5491,7 @@
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>2023-08-23</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="V76" t="inlineStr"/>
@@ -4779,21 +5505,31 @@
       <c r="AD76" t="inlineStr"/>
       <c r="AE76" t="inlineStr"/>
       <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="inlineStr"/>
+      <c r="AH76" t="inlineStr"/>
+      <c r="AI76" t="inlineStr"/>
+      <c r="AJ76" t="inlineStr"/>
+      <c r="AK76" t="inlineStr"/>
+      <c r="AL76" t="inlineStr"/>
+      <c r="AM76" t="inlineStr"/>
+      <c r="AN76" t="inlineStr"/>
+      <c r="AO76" t="inlineStr"/>
+      <c r="AP76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>so:062</t>
+          <t>so:059</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Major ion concentrations: Cl, SO4, Br, Na, K, Mg, Ca, B - groundwater</t>
+          <t>Stable Isotopes (18O, 2H) - groundwater</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>SOHYD_062</t>
+          <t>SOHYD_059</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4802,13 +5538,13 @@
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>so:c3</t>
+        </is>
+      </c>
       <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>so:c3</t>
-        </is>
-      </c>
+      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
@@ -4835,7 +5571,7 @@
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="V77" t="inlineStr"/>
@@ -4849,21 +5585,31 @@
       <c r="AD77" t="inlineStr"/>
       <c r="AE77" t="inlineStr"/>
       <c r="AF77" t="inlineStr"/>
+      <c r="AG77" t="inlineStr"/>
+      <c r="AH77" t="inlineStr"/>
+      <c r="AI77" t="inlineStr"/>
+      <c r="AJ77" t="inlineStr"/>
+      <c r="AK77" t="inlineStr"/>
+      <c r="AL77" t="inlineStr"/>
+      <c r="AM77" t="inlineStr"/>
+      <c r="AN77" t="inlineStr"/>
+      <c r="AO77" t="inlineStr"/>
+      <c r="AP77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>so:064</t>
+          <t>so:062</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Nutrient concentration: TP, SRP, TDN, NO3, NO2, NH4, DOC, DIC - groundwater</t>
+          <t>Major ion concentrations: Cl, SO4, Br, Na, K, Mg, Ca, B - groundwater</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>SOHYD_064</t>
+          <t>SOHYD_062</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4872,13 +5618,13 @@
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>so:c3</t>
+        </is>
+      </c>
       <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>so:c3</t>
-        </is>
-      </c>
+      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
@@ -4905,7 +5651,7 @@
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>2023-08-23</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="V78" t="inlineStr"/>
@@ -4919,21 +5665,31 @@
       <c r="AD78" t="inlineStr"/>
       <c r="AE78" t="inlineStr"/>
       <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="inlineStr"/>
+      <c r="AH78" t="inlineStr"/>
+      <c r="AI78" t="inlineStr"/>
+      <c r="AJ78" t="inlineStr"/>
+      <c r="AK78" t="inlineStr"/>
+      <c r="AL78" t="inlineStr"/>
+      <c r="AM78" t="inlineStr"/>
+      <c r="AN78" t="inlineStr"/>
+      <c r="AO78" t="inlineStr"/>
+      <c r="AP78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>so:164</t>
+          <t>so:064</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Glacier front variation</t>
+          <t>Nutrient concentration: TP, SRP, TDN, NO3, NO2, NH4, DOC, DIC - groundwater</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>SOHYD_164</t>
+          <t>SOHYD_064</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4942,13 +5698,13 @@
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>so:c3</t>
+        </is>
+      </c>
       <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>so:c3</t>
-        </is>
-      </c>
+      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
@@ -4975,7 +5731,7 @@
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>2023-08-23</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="V79" t="inlineStr"/>
@@ -4989,21 +5745,31 @@
       <c r="AD79" t="inlineStr"/>
       <c r="AE79" t="inlineStr"/>
       <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="inlineStr"/>
+      <c r="AH79" t="inlineStr"/>
+      <c r="AI79" t="inlineStr"/>
+      <c r="AJ79" t="inlineStr"/>
+      <c r="AK79" t="inlineStr"/>
+      <c r="AL79" t="inlineStr"/>
+      <c r="AM79" t="inlineStr"/>
+      <c r="AN79" t="inlineStr"/>
+      <c r="AO79" t="inlineStr"/>
+      <c r="AP79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>so:165</t>
+          <t>so:164</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Glacier mass balance</t>
+          <t>Glacier front variation</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>SOHYD_165</t>
+          <t>SOHYD_164</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -5012,13 +5778,13 @@
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>so:c3</t>
+        </is>
+      </c>
       <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>so:c3</t>
-        </is>
-      </c>
+      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
@@ -5045,7 +5811,7 @@
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="V80" t="inlineStr"/>
@@ -5059,21 +5825,31 @@
       <c r="AD80" t="inlineStr"/>
       <c r="AE80" t="inlineStr"/>
       <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="inlineStr"/>
+      <c r="AH80" t="inlineStr"/>
+      <c r="AI80" t="inlineStr"/>
+      <c r="AJ80" t="inlineStr"/>
+      <c r="AK80" t="inlineStr"/>
+      <c r="AL80" t="inlineStr"/>
+      <c r="AM80" t="inlineStr"/>
+      <c r="AN80" t="inlineStr"/>
+      <c r="AO80" t="inlineStr"/>
+      <c r="AP80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>so:166</t>
+          <t>so:165</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Glacier area</t>
+          <t>Glacier mass balance</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>SOHYD_166</t>
+          <t>SOHYD_165</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -5082,13 +5858,13 @@
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>so:c3</t>
+        </is>
+      </c>
       <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>so:c3</t>
-        </is>
-      </c>
+      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
@@ -5115,7 +5891,7 @@
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>2023-08-23</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="V81" t="inlineStr"/>
@@ -5129,21 +5905,31 @@
       <c r="AD81" t="inlineStr"/>
       <c r="AE81" t="inlineStr"/>
       <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="inlineStr"/>
+      <c r="AH81" t="inlineStr"/>
+      <c r="AI81" t="inlineStr"/>
+      <c r="AJ81" t="inlineStr"/>
+      <c r="AK81" t="inlineStr"/>
+      <c r="AL81" t="inlineStr"/>
+      <c r="AM81" t="inlineStr"/>
+      <c r="AN81" t="inlineStr"/>
+      <c r="AO81" t="inlineStr"/>
+      <c r="AP81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>so:168</t>
+          <t>so:166</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Soil water content, soil temperature</t>
+          <t>Glacier area</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>SOHYD_168</t>
+          <t>SOHYD_166</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -5152,13 +5938,13 @@
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>so:c3</t>
+        </is>
+      </c>
       <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>so:c3</t>
-        </is>
-      </c>
+      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
@@ -5185,7 +5971,7 @@
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="V82" t="inlineStr"/>
@@ -5199,21 +5985,31 @@
       <c r="AD82" t="inlineStr"/>
       <c r="AE82" t="inlineStr"/>
       <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="inlineStr"/>
+      <c r="AH82" t="inlineStr"/>
+      <c r="AI82" t="inlineStr"/>
+      <c r="AJ82" t="inlineStr"/>
+      <c r="AK82" t="inlineStr"/>
+      <c r="AL82" t="inlineStr"/>
+      <c r="AM82" t="inlineStr"/>
+      <c r="AN82" t="inlineStr"/>
+      <c r="AO82" t="inlineStr"/>
+      <c r="AP82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>so:169</t>
+          <t>so:168</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Carbon concentration: DOC, DIC - running waters</t>
+          <t>Soil water content, soil temperature</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>SOHYD_169</t>
+          <t>SOHYD_168</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -5222,13 +6018,13 @@
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>so:c3</t>
+        </is>
+      </c>
       <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>so:c3</t>
-        </is>
-      </c>
+      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
@@ -5255,7 +6051,7 @@
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="V83" t="inlineStr"/>
@@ -5269,21 +6065,31 @@
       <c r="AD83" t="inlineStr"/>
       <c r="AE83" t="inlineStr"/>
       <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="inlineStr"/>
+      <c r="AH83" t="inlineStr"/>
+      <c r="AI83" t="inlineStr"/>
+      <c r="AJ83" t="inlineStr"/>
+      <c r="AK83" t="inlineStr"/>
+      <c r="AL83" t="inlineStr"/>
+      <c r="AM83" t="inlineStr"/>
+      <c r="AN83" t="inlineStr"/>
+      <c r="AO83" t="inlineStr"/>
+      <c r="AP83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>so:170</t>
+          <t>so:169</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Profiles of nutrient concentration: DOC, DIC - standing waters</t>
+          <t>Carbon concentration: DOC, DIC - running waters</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>SOHYD_170</t>
+          <t>SOHYD_169</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -5292,13 +6098,13 @@
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>so:c3</t>
+        </is>
+      </c>
       <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>so:c3</t>
-        </is>
-      </c>
+      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
@@ -5325,7 +6131,7 @@
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="V84" t="inlineStr"/>
@@ -5339,21 +6145,31 @@
       <c r="AD84" t="inlineStr"/>
       <c r="AE84" t="inlineStr"/>
       <c r="AF84" t="inlineStr"/>
+      <c r="AG84" t="inlineStr"/>
+      <c r="AH84" t="inlineStr"/>
+      <c r="AI84" t="inlineStr"/>
+      <c r="AJ84" t="inlineStr"/>
+      <c r="AK84" t="inlineStr"/>
+      <c r="AL84" t="inlineStr"/>
+      <c r="AM84" t="inlineStr"/>
+      <c r="AN84" t="inlineStr"/>
+      <c r="AO84" t="inlineStr"/>
+      <c r="AP84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>so:171</t>
+          <t>so:170</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Major ion concentrations: Cl, SO4, Br, Na, K, Mg, Ca, B, Silica - running/standing waters</t>
+          <t>Profiles of nutrient concentration: DOC, DIC - standing waters</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>SOHYD_171</t>
+          <t>SOHYD_170</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -5362,13 +6178,13 @@
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>so:c3</t>
+        </is>
+      </c>
       <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>so:c3</t>
-        </is>
-      </c>
+      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
@@ -5395,7 +6211,7 @@
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="V85" t="inlineStr"/>
@@ -5409,21 +6225,31 @@
       <c r="AD85" t="inlineStr"/>
       <c r="AE85" t="inlineStr"/>
       <c r="AF85" t="inlineStr"/>
+      <c r="AG85" t="inlineStr"/>
+      <c r="AH85" t="inlineStr"/>
+      <c r="AI85" t="inlineStr"/>
+      <c r="AJ85" t="inlineStr"/>
+      <c r="AK85" t="inlineStr"/>
+      <c r="AL85" t="inlineStr"/>
+      <c r="AM85" t="inlineStr"/>
+      <c r="AN85" t="inlineStr"/>
+      <c r="AO85" t="inlineStr"/>
+      <c r="AP85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>so:172</t>
+          <t>so:171</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Nutrient concentration: TP, SRP, TDN, NO3, NO2, NH4 - running waters</t>
+          <t>Major ion concentrations: Cl, SO4, Br, Na, K, Mg, Ca, B, Silica - running/standing waters</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>SOHYD_172</t>
+          <t>SOHYD_171</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5432,13 +6258,13 @@
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>so:c3</t>
+        </is>
+      </c>
       <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>so:c3</t>
-        </is>
-      </c>
+      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
@@ -5465,7 +6291,7 @@
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="V86" t="inlineStr"/>
@@ -5479,21 +6305,31 @@
       <c r="AD86" t="inlineStr"/>
       <c r="AE86" t="inlineStr"/>
       <c r="AF86" t="inlineStr"/>
+      <c r="AG86" t="inlineStr"/>
+      <c r="AH86" t="inlineStr"/>
+      <c r="AI86" t="inlineStr"/>
+      <c r="AJ86" t="inlineStr"/>
+      <c r="AK86" t="inlineStr"/>
+      <c r="AL86" t="inlineStr"/>
+      <c r="AM86" t="inlineStr"/>
+      <c r="AN86" t="inlineStr"/>
+      <c r="AO86" t="inlineStr"/>
+      <c r="AP86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>so:173</t>
+          <t>so:172</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Profiles of nutrient concentration: TP, SRP, TDN, NO3, NO2, NH4 - standing waters</t>
+          <t>Nutrient concentration: TP, SRP, TDN, NO3, NO2, NH4 - running waters</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>SOHYD_173</t>
+          <t>SOHYD_172</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -5502,13 +6338,13 @@
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>so:c3</t>
+        </is>
+      </c>
       <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>so:c3</t>
-        </is>
-      </c>
+      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
@@ -5535,7 +6371,7 @@
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="V87" t="inlineStr"/>
@@ -5549,21 +6385,31 @@
       <c r="AD87" t="inlineStr"/>
       <c r="AE87" t="inlineStr"/>
       <c r="AF87" t="inlineStr"/>
+      <c r="AG87" t="inlineStr"/>
+      <c r="AH87" t="inlineStr"/>
+      <c r="AI87" t="inlineStr"/>
+      <c r="AJ87" t="inlineStr"/>
+      <c r="AK87" t="inlineStr"/>
+      <c r="AL87" t="inlineStr"/>
+      <c r="AM87" t="inlineStr"/>
+      <c r="AN87" t="inlineStr"/>
+      <c r="AO87" t="inlineStr"/>
+      <c r="AP87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>so:174</t>
+          <t>so:173</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Secchi-Depth; standing waters and transitional waters</t>
+          <t>Profiles of nutrient concentration: TP, SRP, TDN, NO3, NO2, NH4 - standing waters</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>SOHYD_174</t>
+          <t>SOHYD_173</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5572,13 +6418,13 @@
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>so:c3</t>
+        </is>
+      </c>
       <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>so:c3</t>
-        </is>
-      </c>
+      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
@@ -5605,7 +6451,7 @@
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="V88" t="inlineStr"/>
@@ -5619,21 +6465,31 @@
       <c r="AD88" t="inlineStr"/>
       <c r="AE88" t="inlineStr"/>
       <c r="AF88" t="inlineStr"/>
+      <c r="AG88" t="inlineStr"/>
+      <c r="AH88" t="inlineStr"/>
+      <c r="AI88" t="inlineStr"/>
+      <c r="AJ88" t="inlineStr"/>
+      <c r="AK88" t="inlineStr"/>
+      <c r="AL88" t="inlineStr"/>
+      <c r="AM88" t="inlineStr"/>
+      <c r="AN88" t="inlineStr"/>
+      <c r="AO88" t="inlineStr"/>
+      <c r="AP88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>so:001</t>
+          <t>so:174</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Soil inventory - pedological/geological characterization</t>
+          <t>Secchi-Depth; standing waters and transitional waters</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>SOGEO_001</t>
+          <t>SOHYD_174</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -5642,23 +6498,19 @@
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>so:c3</t>
+        </is>
+      </c>
       <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>so:c2</t>
-        </is>
-      </c>
+      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr">
-        <is>
-          <t>et:22245,et:22279,et:30319,et:30321,et:30323,et:30324,et:22065,et:22264,et:30067</t>
-        </is>
-      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr"/>
       <c r="P89" t="inlineStr"/>
       <c r="Q89" t="inlineStr"/>
@@ -5679,7 +6531,7 @@
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>2024-01-09</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="V89" t="inlineStr"/>
@@ -5693,38 +6545,56 @@
       <c r="AD89" t="inlineStr"/>
       <c r="AE89" t="inlineStr"/>
       <c r="AF89" t="inlineStr"/>
+      <c r="AG89" t="inlineStr"/>
+      <c r="AH89" t="inlineStr"/>
+      <c r="AI89" t="inlineStr"/>
+      <c r="AJ89" t="inlineStr"/>
+      <c r="AK89" t="inlineStr"/>
+      <c r="AL89" t="inlineStr"/>
+      <c r="AM89" t="inlineStr"/>
+      <c r="AN89" t="inlineStr"/>
+      <c r="AO89" t="inlineStr"/>
+      <c r="AP89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>so:c1</t>
+          <t>so:001</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Sociosphere</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr"/>
+          <t>Soil inventory - pedological/geological characterization</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>SOGEO_001</t>
+        </is>
+      </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>skos:Collection</t>
+          <t>skos:Concept, iop:VariableSet</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>so:c2</t>
+        </is>
+      </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>et:30317</t>
-        </is>
-      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>et:22245,et:22279,et:30319,et:30321,et:30323,et:30324,et:22065,et:22264,et:30067</t>
+        </is>
+      </c>
       <c r="O90" t="inlineStr"/>
       <c r="P90" t="inlineStr"/>
       <c r="Q90" t="inlineStr"/>
@@ -5745,7 +6615,7 @@
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="V90" t="inlineStr"/>
@@ -5759,22 +6629,32 @@
       <c r="AD90" t="inlineStr"/>
       <c r="AE90" t="inlineStr"/>
       <c r="AF90" t="inlineStr"/>
+      <c r="AG90" t="inlineStr"/>
+      <c r="AH90" t="inlineStr"/>
+      <c r="AI90" t="inlineStr"/>
+      <c r="AJ90" t="inlineStr"/>
+      <c r="AK90" t="inlineStr"/>
+      <c r="AL90" t="inlineStr"/>
+      <c r="AM90" t="inlineStr"/>
+      <c r="AN90" t="inlineStr"/>
+      <c r="AO90" t="inlineStr"/>
+      <c r="AP90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>so:c2</t>
+          <t>so:c1</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Geosphere</t>
+          <t>Sociosphere</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
-          <t>skos:Collection</t>
+          <t>skos:Concept</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
@@ -5783,12 +6663,16 @@
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
-          <t>et:30316</t>
+          <t>et:30317</t>
         </is>
       </c>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>so:030, so:031, so:032, so:036, so:037, so:040, so:042, so:043, so:044, so:045, so:114, so:183, so:184</t>
+        </is>
+      </c>
       <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr"/>
@@ -5811,7 +6695,7 @@
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>2023-08-23</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="V91" t="inlineStr"/>
@@ -5825,22 +6709,32 @@
       <c r="AD91" t="inlineStr"/>
       <c r="AE91" t="inlineStr"/>
       <c r="AF91" t="inlineStr"/>
+      <c r="AG91" t="inlineStr"/>
+      <c r="AH91" t="inlineStr"/>
+      <c r="AI91" t="inlineStr"/>
+      <c r="AJ91" t="inlineStr"/>
+      <c r="AK91" t="inlineStr"/>
+      <c r="AL91" t="inlineStr"/>
+      <c r="AM91" t="inlineStr"/>
+      <c r="AN91" t="inlineStr"/>
+      <c r="AO91" t="inlineStr"/>
+      <c r="AP91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>so:c3</t>
+          <t>so:c2</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Hydrosphere</t>
+          <t>Geosphere</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
-          <t>skos:Collection</t>
+          <t>skos:Concept</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
@@ -5849,12 +6743,16 @@
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
-          <t>et:21922</t>
+          <t>et:30316</t>
         </is>
       </c>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>so:001, so:003, so:048, so:155, so:167</t>
+        </is>
+      </c>
       <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr"/>
@@ -5877,7 +6775,7 @@
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>2023-08-23</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="V92" t="inlineStr"/>
@@ -5891,22 +6789,32 @@
       <c r="AD92" t="inlineStr"/>
       <c r="AE92" t="inlineStr"/>
       <c r="AF92" t="inlineStr"/>
+      <c r="AG92" t="inlineStr"/>
+      <c r="AH92" t="inlineStr"/>
+      <c r="AI92" t="inlineStr"/>
+      <c r="AJ92" t="inlineStr"/>
+      <c r="AK92" t="inlineStr"/>
+      <c r="AL92" t="inlineStr"/>
+      <c r="AM92" t="inlineStr"/>
+      <c r="AN92" t="inlineStr"/>
+      <c r="AO92" t="inlineStr"/>
+      <c r="AP92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>so:c4</t>
+          <t>so:c3</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Biosphere</t>
+          <t>Hydrosphere</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
-          <t>skos:Collection</t>
+          <t>skos:Concept</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
@@ -5915,12 +6823,16 @@
       <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
-          <t>et:21921</t>
+          <t>et:21922</t>
         </is>
       </c>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>so:004, so:005, so:006, so:010, so:011, so:012, so:058, so:059, so:062, so:064, so:164, so:165, so:166, so:168, so:169, so:170, so:171, so:172, so:173, so:174</t>
+        </is>
+      </c>
       <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr"/>
@@ -5943,7 +6855,7 @@
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>2023-08-23</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="V93" t="inlineStr"/>
@@ -5957,22 +6869,32 @@
       <c r="AD93" t="inlineStr"/>
       <c r="AE93" t="inlineStr"/>
       <c r="AF93" t="inlineStr"/>
+      <c r="AG93" t="inlineStr"/>
+      <c r="AH93" t="inlineStr"/>
+      <c r="AI93" t="inlineStr"/>
+      <c r="AJ93" t="inlineStr"/>
+      <c r="AK93" t="inlineStr"/>
+      <c r="AL93" t="inlineStr"/>
+      <c r="AM93" t="inlineStr"/>
+      <c r="AN93" t="inlineStr"/>
+      <c r="AO93" t="inlineStr"/>
+      <c r="AP93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>so:c5</t>
+          <t>so:c4</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Atmosphere</t>
+          <t>Biosphere</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
-          <t>skos:Collection</t>
+          <t>skos:Concept</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
@@ -5981,12 +6903,16 @@
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
-          <t>et:21920</t>
+          <t>et:21921</t>
         </is>
       </c>
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>so:014, so:017, so:018, so:019, so:021, so:022, so:096</t>
+        </is>
+      </c>
       <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr"/>
@@ -6009,7 +6935,7 @@
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="V94" t="inlineStr"/>
@@ -6023,40 +6949,50 @@
       <c r="AD94" t="inlineStr"/>
       <c r="AE94" t="inlineStr"/>
       <c r="AF94" t="inlineStr"/>
+      <c r="AG94" t="inlineStr"/>
+      <c r="AH94" t="inlineStr"/>
+      <c r="AI94" t="inlineStr"/>
+      <c r="AJ94" t="inlineStr"/>
+      <c r="AK94" t="inlineStr"/>
+      <c r="AL94" t="inlineStr"/>
+      <c r="AM94" t="inlineStr"/>
+      <c r="AN94" t="inlineStr"/>
+      <c r="AO94" t="inlineStr"/>
+      <c r="AP94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>so:031</t>
+          <t>so:c5</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Yield (cropland, grassland, forest, fishery)</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>SOSOC_031</t>
-        </is>
-      </c>
+          <t>Atmosphere</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
-          <t>skos:Concept, iop:VariableSet</t>
+          <t>skos:Concept</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>so:c1</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>et:21920</t>
+        </is>
+      </c>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>so:015, so:016, so:023, so:024, so:025, so:026, so:027, so:028, so:090, so:091, so:092, so:095, so:098, so:103, so:108, so:140, so:176, so:177</t>
+        </is>
+      </c>
       <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr"/>
@@ -6074,12 +7010,12 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2023-08-16</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="V95" t="inlineStr"/>
@@ -6093,21 +7029,31 @@
       <c r="AD95" t="inlineStr"/>
       <c r="AE95" t="inlineStr"/>
       <c r="AF95" t="inlineStr"/>
+      <c r="AG95" t="inlineStr"/>
+      <c r="AH95" t="inlineStr"/>
+      <c r="AI95" t="inlineStr"/>
+      <c r="AJ95" t="inlineStr"/>
+      <c r="AK95" t="inlineStr"/>
+      <c r="AL95" t="inlineStr"/>
+      <c r="AM95" t="inlineStr"/>
+      <c r="AN95" t="inlineStr"/>
+      <c r="AO95" t="inlineStr"/>
+      <c r="AP95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>so:030</t>
+          <t>so:031</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Land-based income</t>
+          <t>Yield (cropland, grassland, forest, fishery)</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>SOSOC_030</t>
+          <t>SOSOC_031</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -6116,13 +7062,13 @@
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr"/>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>so:c1</t>
+        </is>
+      </c>
       <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>so:c1</t>
-        </is>
-      </c>
+      <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
@@ -6149,7 +7095,7 @@
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="V96" t="inlineStr"/>
@@ -6163,21 +7109,31 @@
       <c r="AD96" t="inlineStr"/>
       <c r="AE96" t="inlineStr"/>
       <c r="AF96" t="inlineStr"/>
+      <c r="AG96" t="inlineStr"/>
+      <c r="AH96" t="inlineStr"/>
+      <c r="AI96" t="inlineStr"/>
+      <c r="AJ96" t="inlineStr"/>
+      <c r="AK96" t="inlineStr"/>
+      <c r="AL96" t="inlineStr"/>
+      <c r="AM96" t="inlineStr"/>
+      <c r="AN96" t="inlineStr"/>
+      <c r="AO96" t="inlineStr"/>
+      <c r="AP96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>so:114</t>
+          <t>so:030</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Livestock</t>
+          <t>Land-based income</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>SOSOC_114</t>
+          <t>SOSOC_030</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -6186,13 +7142,13 @@
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr"/>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>so:c1</t>
+        </is>
+      </c>
       <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>so:c1</t>
-        </is>
-      </c>
+      <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
@@ -6219,7 +7175,7 @@
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="V97" t="inlineStr"/>
@@ -6233,21 +7189,31 @@
       <c r="AD97" t="inlineStr"/>
       <c r="AE97" t="inlineStr"/>
       <c r="AF97" t="inlineStr"/>
+      <c r="AG97" t="inlineStr"/>
+      <c r="AH97" t="inlineStr"/>
+      <c r="AI97" t="inlineStr"/>
+      <c r="AJ97" t="inlineStr"/>
+      <c r="AK97" t="inlineStr"/>
+      <c r="AL97" t="inlineStr"/>
+      <c r="AM97" t="inlineStr"/>
+      <c r="AN97" t="inlineStr"/>
+      <c r="AO97" t="inlineStr"/>
+      <c r="AP97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>so:032</t>
+          <t>so:114</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Governance structure and character</t>
+          <t>Livestock</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>SOSOC_032</t>
+          <t>SOSOC_114</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -6256,13 +7222,13 @@
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>so:c1</t>
+        </is>
+      </c>
       <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>so:c1</t>
-        </is>
-      </c>
+      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
@@ -6289,7 +7255,7 @@
       </c>
       <c r="U98" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="V98" t="inlineStr"/>
@@ -6303,21 +7269,31 @@
       <c r="AD98" t="inlineStr"/>
       <c r="AE98" t="inlineStr"/>
       <c r="AF98" t="inlineStr"/>
+      <c r="AG98" t="inlineStr"/>
+      <c r="AH98" t="inlineStr"/>
+      <c r="AI98" t="inlineStr"/>
+      <c r="AJ98" t="inlineStr"/>
+      <c r="AK98" t="inlineStr"/>
+      <c r="AL98" t="inlineStr"/>
+      <c r="AM98" t="inlineStr"/>
+      <c r="AN98" t="inlineStr"/>
+      <c r="AO98" t="inlineStr"/>
+      <c r="AP98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>so:036</t>
+          <t>so:032</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Land cover, land use, land cover change, land use change - CORINE</t>
+          <t>Governance structure and character</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>SOSOC_036</t>
+          <t>SOSOC_032</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -6326,13 +7302,13 @@
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr"/>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>so:c1</t>
+        </is>
+      </c>
       <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>so:c1</t>
-        </is>
-      </c>
+      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
@@ -6359,7 +7335,7 @@
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="V99" t="inlineStr"/>
@@ -6373,21 +7349,31 @@
       <c r="AD99" t="inlineStr"/>
       <c r="AE99" t="inlineStr"/>
       <c r="AF99" t="inlineStr"/>
+      <c r="AG99" t="inlineStr"/>
+      <c r="AH99" t="inlineStr"/>
+      <c r="AI99" t="inlineStr"/>
+      <c r="AJ99" t="inlineStr"/>
+      <c r="AK99" t="inlineStr"/>
+      <c r="AL99" t="inlineStr"/>
+      <c r="AM99" t="inlineStr"/>
+      <c r="AN99" t="inlineStr"/>
+      <c r="AO99" t="inlineStr"/>
+      <c r="AP99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>so:037</t>
+          <t>so:036</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Land cover, land use, land cover change, land use change (Statistics)</t>
+          <t>Land cover, land use, land cover change, land use change - CORINE</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>SOSOC_037</t>
+          <t>SOSOC_036</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -6396,13 +7382,13 @@
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>so:c1</t>
+        </is>
+      </c>
       <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>so:c1</t>
-        </is>
-      </c>
+      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
@@ -6429,7 +7415,7 @@
       </c>
       <c r="U100" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="V100" t="inlineStr"/>
@@ -6443,21 +7429,31 @@
       <c r="AD100" t="inlineStr"/>
       <c r="AE100" t="inlineStr"/>
       <c r="AF100" t="inlineStr"/>
+      <c r="AG100" t="inlineStr"/>
+      <c r="AH100" t="inlineStr"/>
+      <c r="AI100" t="inlineStr"/>
+      <c r="AJ100" t="inlineStr"/>
+      <c r="AK100" t="inlineStr"/>
+      <c r="AL100" t="inlineStr"/>
+      <c r="AM100" t="inlineStr"/>
+      <c r="AN100" t="inlineStr"/>
+      <c r="AO100" t="inlineStr"/>
+      <c r="AP100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>so:040</t>
+          <t>so:037</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Ecosystem services profile</t>
+          <t>Land cover, land use, land cover change, land use change (Statistics)</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>SOSOC_040</t>
+          <t>SOSOC_037</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -6466,13 +7462,13 @@
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr"/>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>so:c1</t>
+        </is>
+      </c>
       <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>so:c1</t>
-        </is>
-      </c>
+      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
@@ -6499,7 +7495,7 @@
       </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="V101" t="inlineStr"/>
@@ -6513,21 +7509,31 @@
       <c r="AD101" t="inlineStr"/>
       <c r="AE101" t="inlineStr"/>
       <c r="AF101" t="inlineStr"/>
+      <c r="AG101" t="inlineStr"/>
+      <c r="AH101" t="inlineStr"/>
+      <c r="AI101" t="inlineStr"/>
+      <c r="AJ101" t="inlineStr"/>
+      <c r="AK101" t="inlineStr"/>
+      <c r="AL101" t="inlineStr"/>
+      <c r="AM101" t="inlineStr"/>
+      <c r="AN101" t="inlineStr"/>
+      <c r="AO101" t="inlineStr"/>
+      <c r="AP101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>so:042</t>
+          <t>so:040</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Economics (GDP per capita; Per capita income)</t>
+          <t>Ecosystem services profile</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>SOSOC_042</t>
+          <t>SOSOC_040</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -6536,13 +7542,13 @@
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr"/>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>so:c1</t>
+        </is>
+      </c>
       <c r="G102" t="inlineStr"/>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>so:c1</t>
-        </is>
-      </c>
+      <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr"/>
@@ -6569,7 +7575,7 @@
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="V102" t="inlineStr"/>
@@ -6583,21 +7589,31 @@
       <c r="AD102" t="inlineStr"/>
       <c r="AE102" t="inlineStr"/>
       <c r="AF102" t="inlineStr"/>
+      <c r="AG102" t="inlineStr"/>
+      <c r="AH102" t="inlineStr"/>
+      <c r="AI102" t="inlineStr"/>
+      <c r="AJ102" t="inlineStr"/>
+      <c r="AK102" t="inlineStr"/>
+      <c r="AL102" t="inlineStr"/>
+      <c r="AM102" t="inlineStr"/>
+      <c r="AN102" t="inlineStr"/>
+      <c r="AO102" t="inlineStr"/>
+      <c r="AP102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>so:043</t>
+          <t>so:042</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Demography</t>
+          <t>Economics (GDP per capita; Per capita income)</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>SOSOC_043</t>
+          <t>SOSOC_042</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -6606,13 +7622,13 @@
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr"/>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>so:c1</t>
+        </is>
+      </c>
       <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>so:c1</t>
-        </is>
-      </c>
+      <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
@@ -6639,7 +7655,7 @@
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="V103" t="inlineStr"/>
@@ -6653,21 +7669,31 @@
       <c r="AD103" t="inlineStr"/>
       <c r="AE103" t="inlineStr"/>
       <c r="AF103" t="inlineStr"/>
+      <c r="AG103" t="inlineStr"/>
+      <c r="AH103" t="inlineStr"/>
+      <c r="AI103" t="inlineStr"/>
+      <c r="AJ103" t="inlineStr"/>
+      <c r="AK103" t="inlineStr"/>
+      <c r="AL103" t="inlineStr"/>
+      <c r="AM103" t="inlineStr"/>
+      <c r="AN103" t="inlineStr"/>
+      <c r="AO103" t="inlineStr"/>
+      <c r="AP103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>so:044</t>
+          <t>so:043</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Status of employment</t>
+          <t>Demography</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>SOSOC_044</t>
+          <t>SOSOC_043</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -6676,13 +7702,13 @@
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr"/>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>so:c1</t>
+        </is>
+      </c>
       <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>so:c1</t>
-        </is>
-      </c>
+      <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
@@ -6709,7 +7735,7 @@
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="V104" t="inlineStr"/>
@@ -6723,21 +7749,31 @@
       <c r="AD104" t="inlineStr"/>
       <c r="AE104" t="inlineStr"/>
       <c r="AF104" t="inlineStr"/>
+      <c r="AG104" t="inlineStr"/>
+      <c r="AH104" t="inlineStr"/>
+      <c r="AI104" t="inlineStr"/>
+      <c r="AJ104" t="inlineStr"/>
+      <c r="AK104" t="inlineStr"/>
+      <c r="AL104" t="inlineStr"/>
+      <c r="AM104" t="inlineStr"/>
+      <c r="AN104" t="inlineStr"/>
+      <c r="AO104" t="inlineStr"/>
+      <c r="AP104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>so:045</t>
+          <t>so:044</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Population consumption statistics</t>
+          <t>Status of employment</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>SOSOC_045</t>
+          <t>SOSOC_044</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -6746,13 +7782,13 @@
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr"/>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>so:c1</t>
+        </is>
+      </c>
       <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>so:c1</t>
-        </is>
-      </c>
+      <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
@@ -6779,7 +7815,7 @@
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="V105" t="inlineStr"/>
@@ -6793,21 +7829,31 @@
       <c r="AD105" t="inlineStr"/>
       <c r="AE105" t="inlineStr"/>
       <c r="AF105" t="inlineStr"/>
+      <c r="AG105" t="inlineStr"/>
+      <c r="AH105" t="inlineStr"/>
+      <c r="AI105" t="inlineStr"/>
+      <c r="AJ105" t="inlineStr"/>
+      <c r="AK105" t="inlineStr"/>
+      <c r="AL105" t="inlineStr"/>
+      <c r="AM105" t="inlineStr"/>
+      <c r="AN105" t="inlineStr"/>
+      <c r="AO105" t="inlineStr"/>
+      <c r="AP105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>so:183</t>
+          <t>so:045</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Resource use</t>
+          <t>Population consumption statistics</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>SOSOC_183</t>
+          <t>SOSOC_045</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -6816,13 +7862,13 @@
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr"/>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>so:c1</t>
+        </is>
+      </c>
       <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>so:c1</t>
-        </is>
-      </c>
+      <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
@@ -6849,7 +7895,7 @@
       </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="V106" t="inlineStr"/>
@@ -6863,21 +7909,31 @@
       <c r="AD106" t="inlineStr"/>
       <c r="AE106" t="inlineStr"/>
       <c r="AF106" t="inlineStr"/>
+      <c r="AG106" t="inlineStr"/>
+      <c r="AH106" t="inlineStr"/>
+      <c r="AI106" t="inlineStr"/>
+      <c r="AJ106" t="inlineStr"/>
+      <c r="AK106" t="inlineStr"/>
+      <c r="AL106" t="inlineStr"/>
+      <c r="AM106" t="inlineStr"/>
+      <c r="AN106" t="inlineStr"/>
+      <c r="AO106" t="inlineStr"/>
+      <c r="AP106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>so:184</t>
+          <t>so:183</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Subsidies programs / schemas</t>
+          <t>Resource use</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>SOSOC_184</t>
+          <t>SOSOC_183</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -6886,13 +7942,13 @@
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr"/>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>so:c1</t>
+        </is>
+      </c>
       <c r="G107" t="inlineStr"/>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>so:c1</t>
-        </is>
-      </c>
+      <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
@@ -6919,7 +7975,7 @@
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="V107" t="inlineStr"/>
@@ -6933,6 +7989,96 @@
       <c r="AD107" t="inlineStr"/>
       <c r="AE107" t="inlineStr"/>
       <c r="AF107" t="inlineStr"/>
+      <c r="AG107" t="inlineStr"/>
+      <c r="AH107" t="inlineStr"/>
+      <c r="AI107" t="inlineStr"/>
+      <c r="AJ107" t="inlineStr"/>
+      <c r="AK107" t="inlineStr"/>
+      <c r="AL107" t="inlineStr"/>
+      <c r="AM107" t="inlineStr"/>
+      <c r="AN107" t="inlineStr"/>
+      <c r="AO107" t="inlineStr"/>
+      <c r="AP107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>so:184</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Subsidies programs / schemas</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>SOSOC_184</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>skos:Concept, iop:VariableSet</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>so:c1</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
+      <c r="O108" t="inlineStr"/>
+      <c r="P108" t="inlineStr"/>
+      <c r="Q108" t="inlineStr"/>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>http://purl.org/np/RAjk9ru697It_UawXK1gvq-mpaOdGlwyhNb9nF2tfEE2A</t>
+        </is>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0000-0003-2195-3997, https://orcid.org/0000-0002-7997-219X</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr"/>
+      <c r="W108" t="inlineStr"/>
+      <c r="X108" t="inlineStr"/>
+      <c r="Y108" t="inlineStr"/>
+      <c r="Z108" t="inlineStr"/>
+      <c r="AA108" t="inlineStr"/>
+      <c r="AB108" t="inlineStr"/>
+      <c r="AC108" t="inlineStr"/>
+      <c r="AD108" t="inlineStr"/>
+      <c r="AE108" t="inlineStr"/>
+      <c r="AF108" t="inlineStr"/>
+      <c r="AG108" t="inlineStr"/>
+      <c r="AH108" t="inlineStr"/>
+      <c r="AI108" t="inlineStr"/>
+      <c r="AJ108" t="inlineStr"/>
+      <c r="AK108" t="inlineStr"/>
+      <c r="AL108" t="inlineStr"/>
+      <c r="AM108" t="inlineStr"/>
+      <c r="AN108" t="inlineStr"/>
+      <c r="AO108" t="inlineStr"/>
+      <c r="AP108" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
